--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3533.06</v>
+        <v>3566.62</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9279.51</v>
+        <v>9367.66</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4449.84</v>
+        <v>4467.21</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3477.5</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5250.21</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12723.89</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5437.12</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3670.59</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3500.14</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3770.04</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3477.5</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4908.43</v>
+        <v>4927.59</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>67074.3</v>
+        <v>67336.13</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2337.04</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4061.36</v>
+        <v>4102.21</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>47835.83</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7341.18</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8011.34</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3298.79</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10411.24</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>16923.85</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>38308.75</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7681.31</v>
+        <v>7720.45</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24313.46</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2442.08</v>
+        <v>2451.58</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3506.14</v>
+        <v>3519.79</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2492.56</v>
+        <v>2502.26</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6710.74</v>
+        <v>6736.87</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8724.41</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8234.34</v>
+        <v>8192.629999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7289.48</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6446.79</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3733.82</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4295</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5866.27</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3733.82</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5720.37</v>
+        <v>5691.39</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7756.41</v>
+        <v>7717.12</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6398.63</v>
+        <v>6412.27</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11949.35</v>
+        <v>11974.81</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2832.43</v>
+        <v>2838.46</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5330.25</v>
+        <v>5341.61</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>67215.66</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>13195.15</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3205.05</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4061.36</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4075.79</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4061.36</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7543.72</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10838.87</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4024.91</v>
+        <v>4034.14</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>42820.93</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2347.87</v>
+        <v>2363.58</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>14717.83</v>
+        <v>14816.35</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4090.36</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>17447.93</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2683.93</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4177.28</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6265.2</v>
+        <v>6309.05</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11949.35</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9279.51</v>
+        <v>9344.450000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>73626.42999999999</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4211.23</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4295</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6343.69</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13498.18</v>
+        <v>13455.54</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3733.82</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>47450.7</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4415.74</v>
+        <v>4406.13</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5460.62</v>
+        <v>5448.74</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>11687.12</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4315.43</v>
+        <v>4306.04</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10411.24</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>57719.28</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>55328.92</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>27763.77</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3908.56</v>
+        <v>3900.73</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>20785.19</v>
+        <v>20743.53</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>72323.72</v>
+        <v>71905.10000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>45742.47</v>
+        <v>45477.7</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4358.79</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2684.3</v>
+        <v>2640.98</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>9026.91</v>
+        <v>8882.17</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2400.44</v>
+        <v>2361.95</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2501.94</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4115.92</v>
+        <v>4049.93</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3354.09</v>
+        <v>3300.31</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5648.29</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>40097.65</v>
+        <v>39454.74</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>69079.46000000001</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2770.58</v>
+        <v>2738.34</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>25594.53</v>
+        <v>25296.72</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3521.8</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>45617.07</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2585.87</v>
+        <v>2573.16</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>20550.59</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10211.24</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3201.42</v>
+        <v>3185.68</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>16151.69</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6022.45</v>
+        <v>6062.76</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>25140.58</v>
+        <v>25308.85</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>49391.07</v>
+        <v>49721.66</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3477.5</v>
+        <v>3500.77</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5299.59</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3298.79</v>
+        <v>3320.87</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>20124.56</v>
+        <v>20259.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Productos Medicos Limitada</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -1782,7 +1782,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1847,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2339,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2465,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3262,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3632,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3697,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3762,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3888,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5356,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5848,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6218,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7015,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -1721,7 +1721,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2896,7 +2900,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4075,7 +4083,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4319,7 +4331,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4685,7 +4701,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4990,7 +5010,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5787,7 +5811,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6157,7 +6185,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6771,7 +6803,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057539-5011-CM26</t>
+          <t>1380-8310-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,53 +651,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4467.21</v>
+        <v>15045.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2111-10243-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,17 +721,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +741,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +756,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3491.07</v>
+        <v>10907.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>1057539-5011-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,22 +782,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5270.71</v>
+        <v>4467.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>12773.56</v>
+        <v>3684.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5458.34</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3684.92</v>
+        <v>5270.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1057,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3513.8</v>
+        <v>12773.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3784.76</v>
+        <v>2346.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3491.07</v>
+        <v>5458.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1691-1231-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,27 +1214,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4927.59</v>
+        <v>3784.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057431-1636-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,22 +1270,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.295-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>67336.13</v>
+        <v>3491.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2111-9684-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1331,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2346.16</v>
+        <v>10907.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3378-5622-CM26</t>
+          <t>1691-1231-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,27 +1397,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4102.21</v>
+        <v>4927.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5326-867-CM26</t>
+          <t>2111-9619-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1448,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,27 +1458,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>48316.94</v>
+        <v>3272.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>1057431-1636-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1509,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,17 +1519,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.295-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1545,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7414.69</v>
+        <v>67336.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1606,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8091.56</v>
+        <v>3513.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>3378-5622-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1631,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3331.82</v>
+        <v>4102.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>5326-867-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,57 +1692,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.400.383-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>10464.29</v>
+        <v>48316.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1753,57 +1753,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>17010.09</v>
+        <v>7414.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1818,57 +1814,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>38503.97</v>
+        <v>8091.56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1057539-5169-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1883,27 +1875,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1923,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7720.45</v>
+        <v>3331.82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057489-8316-CM26</t>
+          <t>1057539-5169-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1944,37 +1936,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1984,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>24408.11</v>
+        <v>7720.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3391-455-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2015,43 +2007,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2451.58</v>
+        <v>38503.97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1057539-5087-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,53 +2062,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3519.79</v>
+        <v>10464.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4967-1297-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2137,37 +2137,41 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2502.26</v>
+        <v>17010.09</v>
       </c>
     </row>
     <row r="29">
@@ -2234,7 +2238,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>4967-1297-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2259,27 +2263,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2289,13 +2293,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8758.370000000001</v>
+        <v>2502.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057439-4572-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2310,7 +2314,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2320,47 +2324,43 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8192.629999999999</v>
+        <v>8758.370000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1057539-5087-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2375,37 +2375,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7252.55</v>
+        <v>3519.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>3391-455-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2446,47 +2446,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6414.13</v>
+        <v>2451.58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057489-8316-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2501,7 +2497,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2511,17 +2507,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2541,13 +2537,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3714.9</v>
+        <v>24408.11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2602,13 +2598,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4273.24</v>
+        <v>5836.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1063538-5042-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2633,27 +2629,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5836.56</v>
+        <v>7717.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1057439-4572-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2694,37 +2690,41 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3714.9</v>
+        <v>8192.629999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2791,7 +2791,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1063538-5042-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2816,27 +2816,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2846,13 +2846,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7717.12</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3191-3409-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2867,57 +2867,53 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6412.27</v>
+        <v>4273.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057491-4113-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2942,27 +2938,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2972,13 +2968,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>11974.81</v>
+        <v>3714.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3391-464-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2993,53 +2989,57 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2838.46</v>
+        <v>6414.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057417-13650-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3064,27 +3064,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3094,13 +3094,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5341.61</v>
+        <v>7252.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1549-3011-CM26</t>
+          <t>1057417-13650-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3115,37 +3115,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3155,13 +3155,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>67653.86</v>
+        <v>5341.61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>3391-464-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3186,17 +3186,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>13225.4</v>
+        <v>2838.46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057539-5481-CM26</t>
+          <t>1057491-4113-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3237,57 +3237,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3212.4</v>
+        <v>11974.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3391-467-CM26</t>
+          <t>3191-3409-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3302,7 +3298,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3312,43 +3308,47 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4070.68</v>
+        <v>6412.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>1549-3011-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4085.13</v>
+        <v>67653.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>3391-467-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3470,7 +3470,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3525,13 +3525,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7561.02</v>
+        <v>13225.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>1057539-5481-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3556,43 +3556,47 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10863.72</v>
+        <v>3212.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1691-1273-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3617,47 +3621,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4034.14</v>
+        <v>4085.13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3677,17 +3677,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3697,32 +3697,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>42919.12</v>
+        <v>4070.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5349-1405-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3737,7 +3733,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3747,47 +3743,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2363.58</v>
+        <v>7561.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057503-3492-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,22 +3794,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3827,12 +3819,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3842,13 +3834,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>14816.35</v>
+        <v>10863.72</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>1691-1273-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3863,37 +3855,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3907,13 +3899,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4117.74</v>
+        <v>4034.14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3928,7 +3920,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3938,12 +3930,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3953,28 +3945,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>17570.04</v>
+        <v>42919.12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>1057503-3492-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3989,22 +3985,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4029,13 +4025,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2702.72</v>
+        <v>14816.35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4050,22 +4046,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4075,12 +4071,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4094,13 +4090,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>4206.51</v>
+        <v>4117.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1075337-8967-CM26</t>
+          <t>5349-1405-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4115,53 +4111,57 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6309.05</v>
+        <v>2363.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>12032.97</v>
+        <v>17570.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1063538-5132-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4242,32 +4242,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SPINEX CORPORATION CHILE S.A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9344.450000000001</v>
+        <v>2702.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057501-7879-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4298,22 +4298,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>73393.87</v>
+        <v>4206.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>1075337-8967-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4373,27 +4373,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4403,13 +4403,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4197.93</v>
+        <v>6309.05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4434,27 +4434,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4281.44</v>
+        <v>12032.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>1063538-5132-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4485,37 +4485,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SPINEX CORPORATION CHILE S.A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6323.65</v>
+        <v>9344.450000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1691-1379-CM26</t>
+          <t>1057501-7879-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4551,48 +4551,52 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13455.54</v>
+        <v>73393.87</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4647,13 +4651,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3722.02</v>
+        <v>4281.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4668,57 +4672,53 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>47347.46</v>
+        <v>4197.93</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3328-1722-CM26</t>
+          <t>1691-1379-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4743,27 +4743,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>4406.13</v>
+        <v>13455.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3328-1751-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4804,27 +4804,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4834,13 +4834,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5448.74</v>
+        <v>6323.65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057539-5660-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4855,37 +4855,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>11661.69</v>
+        <v>3722.02</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1430708-120-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4921,48 +4921,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4306.04</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>3328-1722-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4977,7 +4981,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4987,12 +4991,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5002,32 +5006,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>10390.37</v>
+        <v>4406.13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>3328-1751-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5082,13 +5082,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>57603.57</v>
+        <v>5448.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>1057539-5660-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5143,13 +5143,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>55218.01</v>
+        <v>11661.69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>1430708-120-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5164,27 +5164,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>27708.12</v>
+        <v>4306.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057402-7716-CM26</t>
+          <t>2080-7102-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5235,27 +5235,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3900.73</v>
+        <v>9406.209999999999</v>
       </c>
     </row>
     <row r="79">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5332,7 +5332,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057539-5748-CM26</t>
+          <t>1057402-7716-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5347,57 +5347,53 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>71905.10000000001</v>
+        <v>3900.73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1952-1929-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5412,53 +5408,57 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>45477.7</v>
+        <v>10390.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>608-7408-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5473,37 +5473,37 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4288.45</v>
+        <v>55218.01</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2111-10881-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5534,22 +5534,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5574,13 +5574,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2640.98</v>
+        <v>57603.57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2107-1497-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5595,37 +5595,37 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5635,13 +5635,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8882.17</v>
+        <v>27708.12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057509-8182-CM26</t>
+          <t>1952-1929-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5666,27 +5666,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5696,13 +5696,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2361.95</v>
+        <v>45477.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>1057539-5748-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5717,53 +5717,57 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2461.82</v>
+        <v>71905.10000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4502-682-CM26</t>
+          <t>608-7408-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5788,47 +5792,43 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4049.93</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2258-6051-CM26</t>
+          <t>2111-10881-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5843,57 +5843,53 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3300.31</v>
+        <v>2640.98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>886954-3488-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5918,27 +5914,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5948,13 +5944,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5557.72</v>
+        <v>39454.74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>886954-3488-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5974,32 +5970,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -6009,13 +6005,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>39454.74</v>
+        <v>5557.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>2258-6051-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6035,48 +6031,52 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>67971.87</v>
+        <v>3300.31</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4776-382-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2738.34</v>
+        <v>67971.87</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3191-3857-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6152,57 +6152,53 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>25296.72</v>
+        <v>2461.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>1057509-8182-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6217,7 +6213,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6227,47 +6223,43 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3502.27</v>
+        <v>2361.95</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>4502-682-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6282,7 +6274,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6292,43 +6284,47 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>45364.17</v>
+        <v>4049.93</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>2107-1497-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6343,37 +6339,37 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6383,13 +6379,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2573.16</v>
+        <v>8882.17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2258-5597-CM26</t>
+          <t>3191-3857-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6404,53 +6400,57 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>20449.55</v>
+        <v>25296.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2258-5681-CM26</t>
+          <t>4776-382-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6475,27 +6475,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6505,13 +6505,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10161.04</v>
+        <v>2738.34</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5083-376-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6526,53 +6526,57 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3185.68</v>
+        <v>3502.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6587,27 +6591,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6627,13 +6631,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>16072.28</v>
+        <v>45364.17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1057501-8311-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6648,7 +6652,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6658,27 +6662,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6688,13 +6692,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6062.76</v>
+        <v>20449.55</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2080-7285-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6709,37 +6713,37 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6749,13 +6753,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>25308.85</v>
+        <v>10161.04</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1549-3347-CM26</t>
+          <t>5083-376-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6770,7 +6774,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6780,47 +6784,43 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>49721.66</v>
+        <v>3185.68</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6835,37 +6835,37 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3500.77</v>
+        <v>2573.16</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6896,27 +6896,27 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6936,13 +6936,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5335.07</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2069-6759-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6997,72 +6997,442 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3320.87</v>
+        <v>5335.07</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>2069-6748-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>3500.77</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2069-6759-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>3320.87</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2080-7285-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>78.073.910-k</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>25308.85</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1057501-8311-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.608.502-6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>6062.76</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1549-3347-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>49721.66</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>3328-1937-CM26</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>61.103.007-K</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="n">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
         <v>20259.26</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>5083-398-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>3349.21</v>
       </c>
     </row>
   </sheetData>
